--- a/readme_files/bootloader_summary.xlsx
+++ b/readme_files/bootloader_summary.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\temp\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AC6104-58D1-4559-A6CC-18938B5E1A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="1050" windowWidth="21600" windowHeight="14175" activeTab="1" xr2:uid="{6C55A1A0-E8E8-4669-A1BD-2E037FD69E57}"/>
+    <workbookView xWindow="3045" yWindow="1050" windowWidth="21600" windowHeight="14175" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'2'!$A$1:$J$24</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="110">
   <si>
     <t>bootloader_platformio</t>
   </si>
@@ -346,12 +340,27 @@
   </si>
   <si>
     <t>SDIO_F407VE_fatfs-stm32-master</t>
+  </si>
+  <si>
+    <t>SDIO_F446ZE_fatfs-stm32-master</t>
+  </si>
+  <si>
+    <t>3E78</t>
+  </si>
+  <si>
+    <t>BTT Octopus V1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The factory load point  is 0x8080000.  </t>
+  </si>
+  <si>
+    <t>STM32F446ZE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -747,14 +756,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9380BF52-50BC-4D60-860D-CA620E9C6C42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1351,7 +1360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA31013B-D0F5-4B09-BDE8-13045777ACA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1501,6 +1510,23 @@
         <v>71</v>
       </c>
     </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+    </row>
     <row r="10" spans="1:13" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="10" t="s">
         <v>80</v>
@@ -1740,8 +1766,25 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C24" s="9"/>
+    <row r="24" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="14">
+        <v>8004000</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C25" s="9"/>

--- a/readme_files/bootloader_summary.xlsx
+++ b/readme_files/bootloader_summary.xlsx
@@ -345,9 +345,6 @@
     <t>SDIO_F446ZE_fatfs-stm32-master</t>
   </si>
   <si>
-    <t>3E78</t>
-  </si>
-  <si>
     <t>BTT Octopus V1.1</t>
   </si>
   <si>
@@ -355,6 +352,9 @@
   </si>
   <si>
     <t>STM32F446ZE</t>
+  </si>
+  <si>
+    <t>3EC8</t>
   </si>
 </sst>
 </file>
@@ -756,7 +756,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
         <v>29</v>
@@ -1774,16 +1774,16 @@
         <v>105</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D24" s="14">
         <v>8004000</v>
       </c>
       <c r="E24" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" s="12" t="s">
         <v>107</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
